--- a/data/trans_orig/P57C2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57C2_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se ha sentido bien consigo mismo/a en 2023</t>
+          <t>Población según si se ha sentido bien consigo mismo/a en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27405</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22563</t>
+          <t>22946</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23600</t>
+          <t>24145</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44067</t>
+          <t>43766</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>240761</t>
+          <t>238129</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>270823</t>
+          <t>268830</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>226488</t>
+          <t>225789</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>247328</t>
+          <t>245801</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>473469</t>
+          <t>474046</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>510636</t>
+          <t>511448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26605</t>
+          <t>25676</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51909</t>
+          <t>51691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25548</t>
+          <t>25752</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42374</t>
+          <t>42539</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56368</t>
+          <t>56531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87365</t>
+          <t>85493</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>7937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>11036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21492</t>
+          <t>21460</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30438</t>
+          <t>28830</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21010</t>
+          <t>21157</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50567</t>
+          <t>50605</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36850</t>
+          <t>34745</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58197</t>
+          <t>56779</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61401</t>
+          <t>63201</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>99454</t>
+          <t>101384</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>240959</t>
+          <t>247104</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>298693</t>
+          <t>305907</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>278120</t>
+          <t>279027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>317477</t>
+          <t>320215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>534343</t>
+          <t>533218</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>607133</t>
+          <t>607969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174683</t>
+          <t>166785</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>233595</t>
+          <t>226758</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138788</t>
+          <t>138688</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177438</t>
+          <t>176543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>322823</t>
+          <t>324980</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>393022</t>
+          <t>395402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>10528</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10395</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17323</t>
+          <t>17291</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21166</t>
+          <t>20960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10376</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21531</t>
+          <t>21733</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20769</t>
+          <t>20672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>39115</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25956</t>
+          <t>24736</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48114</t>
+          <t>46833</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32142</t>
+          <t>32385</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53200</t>
+          <t>54400</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63549</t>
+          <t>63042</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>94646</t>
+          <t>92848</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91693</t>
+          <t>92735</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123095</t>
+          <t>126802</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>122980</t>
+          <t>123320</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>152477</t>
+          <t>153816</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>222403</t>
+          <t>224048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>267969</t>
+          <t>270829</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>136781</t>
+          <t>136519</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>171696</t>
+          <t>171169</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>130110</t>
+          <t>131878</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>162108</t>
+          <t>162976</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>275634</t>
+          <t>274845</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>322045</t>
+          <t>323898</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21734</t>
+          <t>23653</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27133</t>
+          <t>25827</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16074</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42298</t>
+          <t>43475</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>2463</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>13844</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22018</t>
+          <t>21947</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12733</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>30589</t>
+          <t>29558</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36425</t>
+          <t>35256</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63007</t>
+          <t>62638</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38021</t>
+          <t>41298</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84165</t>
+          <t>86771</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>84238</t>
+          <t>83029</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>136879</t>
+          <t>137006</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55064</t>
+          <t>54904</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90038</t>
+          <t>89569</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87179</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>201427</t>
+          <t>205849</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>159958</t>
+          <t>162435</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>284694</t>
+          <t>283646</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>151754</t>
+          <t>153637</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>196254</t>
+          <t>195577</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>187684</t>
+          <t>188988</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>321468</t>
+          <t>334372</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>354493</t>
+          <t>361073</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>508459</t>
+          <t>520118</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>66,09%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15275</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21931</t>
+          <t>21444</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>6499</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15946</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8366</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>17021</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17143</t>
+          <t>17084</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29683</t>
+          <t>29722</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>124850</t>
+          <t>124586</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>145503</t>
+          <t>145093</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>157359</t>
+          <t>156079</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>173974</t>
+          <t>173761</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>289187</t>
+          <t>287636</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>314763</t>
+          <t>314405</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,24%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>17487</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>35589</t>
+          <t>35967</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>14218</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27670</t>
+          <t>28665</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>35366</t>
+          <t>35805</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>57848</t>
+          <t>57875</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>15224</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16378</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19151</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16970</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>31516</t>
+          <t>31028</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>22354</t>
+          <t>22196</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>39529</t>
+          <t>39664</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>28553</t>
+          <t>28959</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>43845</t>
+          <t>44316</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>54854</t>
+          <t>54830</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>78047</t>
+          <t>78457</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>98701</t>
+          <t>97060</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>128719</t>
+          <t>127203</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>94484</t>
+          <t>95385</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>120328</t>
+          <t>119465</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>200461</t>
+          <t>200094</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>240049</t>
+          <t>239533</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,48%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>95684</t>
+          <t>96037</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>126721</t>
+          <t>127094</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>84583</t>
+          <t>84790</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>110227</t>
+          <t>110202</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>189990</t>
+          <t>189374</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>228803</t>
+          <t>230851</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>22607</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>29529</t>
+          <t>29345</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>20559</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>28770</t>
+          <t>28381</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>17958</t>
+          <t>17021</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>41503</t>
+          <t>42402</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26773</t>
+          <t>27131</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>17154</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>55627</t>
+          <t>55556</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>31786</t>
+          <t>33962</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>71861</t>
+          <t>72561</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>266190</t>
+          <t>267515</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>327527</t>
+          <t>327734</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>383909</t>
+          <t>384449</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>675217</t>
+          <t>672573</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>681449</t>
+          <t>681416</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1042409</t>
+          <t>1014463</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>68,88%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>261824</t>
+          <t>261558</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>323183</t>
+          <t>324286</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>138119</t>
+          <t>137213</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>375947</t>
+          <t>377659</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>370273</t>
+          <t>387933</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>675921</t>
+          <t>672744</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>16796</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>13340</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>24181</t>
+          <t>25023</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>15307</t>
+          <t>17431</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>53427</t>
+          <t>54794</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>54860</t>
+          <t>54339</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>78476</t>
+          <t>77453</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>63763</t>
+          <t>59667</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>128119</t>
+          <t>125624</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>37361</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>124675</t>
+          <t>126971</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>113322</t>
+          <t>113486</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>147605</t>
+          <t>148405</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>130932</t>
+          <t>135368</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>261930</t>
+          <t>265543</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>108739</t>
+          <t>113962</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>343439</t>
+          <t>343811</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>227448</t>
+          <t>226236</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>269701</t>
+          <t>268877</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>291860</t>
+          <t>302475</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>589490</t>
+          <t>587631</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>406666</t>
+          <t>406833</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>761954</t>
+          <t>753731</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>241543</t>
+          <t>244774</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>289873</t>
+          <t>290886</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>662090</t>
+          <t>662366</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1139615</t>
+          <t>1136943</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>26604</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>54883</t>
+          <t>55726</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>33102</t>
+          <t>34734</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>61712</t>
+          <t>62830</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>66397</t>
+          <t>68869</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>106374</t>
+          <t>107934</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>72639</t>
+          <t>70990</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>116190</t>
+          <t>113087</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>117397</t>
+          <t>117838</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>168718</t>
+          <t>169300</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>199827</t>
+          <t>199289</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>266420</t>
+          <t>268386</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>216855</t>
+          <t>218882</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>316633</t>
+          <t>317770</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>316667</t>
+          <t>312078</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>427922</t>
+          <t>427172</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>574294</t>
+          <t>574616</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>723130</t>
+          <t>724636</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1155429</t>
+          <t>1135032</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1638418</t>
+          <t>1636233</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1693005</t>
+          <t>1696913</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>2132488</t>
+          <t>2165482</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3023131</t>
+          <t>3023394</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3635967</t>
+          <t>3656725</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,44%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1380322</t>
+          <t>1379554</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1975948</t>
+          <t>2002004</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1044372</t>
+          <t>1055393</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1370878</t>
+          <t>1382655</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2543893</t>
+          <t>2528757</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3260406</t>
+          <t>3237245</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57C2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57C2_2023-Provincia-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>9631</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27842</t>
+          <t>24752</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16512</t>
+          <t>18993</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22946</t>
+          <t>24852</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>34258</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24145</t>
+          <t>26186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43766</t>
+          <t>44123</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>256195</t>
+          <t>258670</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>238129</t>
+          <t>244826</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>268830</t>
+          <t>271705</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>236849</t>
+          <t>249993</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>225789</t>
+          <t>238409</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>245801</t>
+          <t>261048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>493042</t>
+          <t>508663</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>474046</t>
+          <t>490226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>511448</t>
+          <t>526090</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>82,86%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>37059</t>
+          <t>43666</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25676</t>
+          <t>32898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51691</t>
+          <t>57156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>33181</t>
+          <t>43601</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25752</t>
+          <t>34512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42539</t>
+          <t>56152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>70239</t>
+          <t>87267</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56531</t>
+          <t>72844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85493</t>
+          <t>104579</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>7702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21460</t>
+          <t>20785</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>16041</t>
+          <t>16169</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28830</t>
+          <t>28337</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33680</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21157</t>
+          <t>22732</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>52519</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45680</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34745</t>
+          <t>36649</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56779</t>
+          <t>59911</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>79360</t>
+          <t>82676</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63201</t>
+          <t>65880</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>101384</t>
+          <t>102517</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>273166</t>
+          <t>278836</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>247104</t>
+          <t>247917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>305907</t>
+          <t>304935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>297349</t>
+          <t>315869</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>279027</t>
+          <t>295273</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>320215</t>
+          <t>336140</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>570515</t>
+          <t>594704</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>533218</t>
+          <t>557357</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>607969</t>
+          <t>630242</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,83%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>200013</t>
+          <t>205214</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166785</t>
+          <t>179856</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226758</t>
+          <t>236907</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>157893</t>
+          <t>168826</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138688</t>
+          <t>150419</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176543</t>
+          <t>189524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>357907</t>
+          <t>374040</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>324980</t>
+          <t>339781</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>395402</t>
+          <t>411342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,4%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>510212</t>
+          <t>541548</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>510212</t>
+          <t>541548</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>510212</t>
+          <t>541548</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1027605</t>
+          <t>1071207</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1027605</t>
+          <t>1071207</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1027605</t>
+          <t>1071207</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,102 +2089,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10528</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5894</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2937</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>10508</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>10701</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>6323</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>18272</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5760</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2948</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>10395</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>10767</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>6039</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>17291</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>22435</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21733</t>
+          <t>23475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>28077</t>
+          <t>29714</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20672</t>
+          <t>21617</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39115</t>
+          <t>40409</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34580</t>
+          <t>36142</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24736</t>
+          <t>26659</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46833</t>
+          <t>47770</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41925</t>
+          <t>42185</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32385</t>
+          <t>32881</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54400</t>
+          <t>54729</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>76505</t>
+          <t>78327</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63042</t>
+          <t>65608</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92848</t>
+          <t>95409</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>107627</t>
+          <t>107036</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92735</t>
+          <t>92088</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>126802</t>
+          <t>124006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>138114</t>
+          <t>141247</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>123320</t>
+          <t>125822</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>153816</t>
+          <t>156554</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>245741</t>
+          <t>248283</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>224048</t>
+          <t>229858</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>270829</t>
+          <t>273322</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>153996</t>
+          <t>152898</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>136519</t>
+          <t>134393</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>171169</t>
+          <t>169190</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>146127</t>
+          <t>148599</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>131878</t>
+          <t>131907</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>162976</t>
+          <t>163867</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>300124</t>
+          <t>301496</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>274845</t>
+          <t>275747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>323898</t>
+          <t>323709</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,42%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>313777</t>
+          <t>313849</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>313777</t>
+          <t>313849</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>313777</t>
+          <t>313849</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>347435</t>
+          <t>354672</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>347435</t>
+          <t>354672</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>347435</t>
+          <t>354672</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>661213</t>
+          <t>668521</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>661213</t>
+          <t>668521</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>661213</t>
+          <t>668521</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12098</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>27014</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25827</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>26499</t>
+          <t>29155</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>19193</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43475</t>
+          <t>45669</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>14597</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21947</t>
+          <t>22192</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29558</t>
+          <t>30699</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>47775</t>
+          <t>59752</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35256</t>
+          <t>43999</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>62638</t>
+          <t>79186</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>65164</t>
+          <t>72930</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>41298</t>
+          <t>61844</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86771</t>
+          <t>87437</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>112939</t>
+          <t>132682</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>83029</t>
+          <t>113251</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>137006</t>
+          <t>157829</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>71570</t>
+          <t>77431</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54904</t>
+          <t>59268</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>89569</t>
+          <t>95867</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>138306</t>
+          <t>120359</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>103127</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>205849</t>
+          <t>137100</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>209875</t>
+          <t>197790</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>162435</t>
+          <t>173817</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>283646</t>
+          <t>224639</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>173920</t>
+          <t>214743</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>153637</t>
+          <t>190811</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>195577</t>
+          <t>239312</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>243385</t>
+          <t>197603</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>188988</t>
+          <t>177681</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>334372</t>
+          <t>217003</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>417305</t>
+          <t>412345</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>361073</t>
+          <t>377780</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>520118</t>
+          <t>444635</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>56,02%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>311963</t>
+          <t>372474</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>311963</t>
+          <t>372474</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>311963</t>
+          <t>372474</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>474979</t>
+          <t>421216</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>474979</t>
+          <t>421216</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>474979</t>
+          <t>421216</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>786941</t>
+          <t>793689</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>786941</t>
+          <t>793689</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>786941</t>
+          <t>793689</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>916</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>780</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,22 +3601,22 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9189</t>
+          <t>10168</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>17255</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>16083</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21444</t>
+          <t>23383</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>11919</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>18204</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17021</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>19207</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29722</t>
+          <t>33108</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>135811</t>
+          <t>153736</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>124586</t>
+          <t>141502</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>145093</t>
+          <t>163435</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>166123</t>
+          <t>180814</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>156079</t>
+          <t>170191</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>173761</t>
+          <t>188957</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>301934</t>
+          <t>334550</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>287636</t>
+          <t>318698</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>314405</t>
+          <t>347912</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>25525</t>
+          <t>32573</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>17487</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>35967</t>
+          <t>43176</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>19908</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14218</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28665</t>
+          <t>29692</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>45434</t>
+          <t>53767</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>35805</t>
+          <t>42388</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>57875</t>
+          <t>68033</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15224</t>
+          <t>14593</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>17711</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>13074</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>22965</t>
+          <t>24351</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>31028</t>
+          <t>32775</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>32026</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>22196</t>
+          <t>24094</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>39664</t>
+          <t>41524</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>35838</t>
+          <t>38210</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>28959</t>
+          <t>30982</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>44316</t>
+          <t>47149</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>65826</t>
+          <t>70237</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>54830</t>
+          <t>58746</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>78457</t>
+          <t>83155</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>112799</t>
+          <t>114506</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>97060</t>
+          <t>99717</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>127203</t>
+          <t>128846</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>106593</t>
+          <t>109520</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>95385</t>
+          <t>96563</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>119465</t>
+          <t>121909</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>219392</t>
+          <t>224026</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>200094</t>
+          <t>203667</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>239533</t>
+          <t>241559</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>112059</t>
+          <t>108373</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>96037</t>
+          <t>93747</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>127094</t>
+          <t>123872</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>97785</t>
+          <t>98934</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>84790</t>
+          <t>85876</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>110202</t>
+          <t>112231</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>209844</t>
+          <t>207307</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>189374</t>
+          <t>188755</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>230851</t>
+          <t>227883</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,102 +4817,102 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>14006</t>
+          <t>13213</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>7381</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>25144</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>19732</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>11746</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>33367</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>11420</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>4446</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>21654</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>17439</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>9678</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>29345</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>12794</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>20559</t>
+          <t>21662</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>22715</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>13194</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>28381</t>
+          <t>34557</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>29106</t>
+          <t>35510</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>17021</t>
+          <t>25426</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>42402</t>
+          <t>48728</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>17089</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>27131</t>
+          <t>32880</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>37622</t>
+          <t>43014</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>14965</t>
+          <t>32134</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>55556</t>
+          <t>57916</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>54711</t>
+          <t>64550</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>33962</t>
+          <t>52151</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>72561</t>
+          <t>84487</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>297144</t>
+          <t>339552</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>267515</t>
+          <t>306795</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>327734</t>
+          <t>369431</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>504030</t>
+          <t>352435</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>384449</t>
+          <t>327095</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>672573</t>
+          <t>380637</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>801175</t>
+          <t>691987</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>681416</t>
+          <t>650159</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1014463</t>
+          <t>734376</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>49,25%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>291783</t>
+          <t>339673</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>261558</t>
+          <t>309181</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>324286</t>
+          <t>372063</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>278688</t>
+          <t>339602</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>137213</t>
+          <t>311454</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>377659</t>
+          <t>364154</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>570471</t>
+          <t>679275</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>387933</t>
+          <t>636113</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>672744</t>
+          <t>721807</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>848623</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>848623</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>848623</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1472902</t>
+          <t>1491053</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1472902</t>
+          <t>1491053</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1472902</t>
+          <t>1491053</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>16796</t>
+          <t>19490</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>25023</t>
+          <t>30603</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>35767</t>
+          <t>40036</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>30034</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>54794</t>
+          <t>52784</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,22 +5647,22 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>65351</t>
+          <t>76272</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>54339</t>
+          <t>62934</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>77453</t>
+          <t>90862</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>101118</t>
+          <t>116308</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>59667</t>
+          <t>97260</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>125624</t>
+          <t>134726</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>86698</t>
+          <t>98005</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>39364</t>
+          <t>81985</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>126971</t>
+          <t>119522</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>130840</t>
+          <t>152833</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>113486</t>
+          <t>134994</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>148405</t>
+          <t>174017</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>217538</t>
+          <t>250838</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>135368</t>
+          <t>224807</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>265543</t>
+          <t>279253</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>244486</t>
+          <t>285300</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>113962</t>
+          <t>256653</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>343811</t>
+          <t>313229</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>248222</t>
+          <t>292529</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>226236</t>
+          <t>269322</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>268877</t>
+          <t>317036</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>492708</t>
+          <t>577828</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>302475</t>
+          <t>540304</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>587631</t>
+          <t>615112</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>553166</t>
+          <t>363525</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>406833</t>
+          <t>334032</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>753731</t>
+          <t>397135</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>265095</t>
+          <t>299923</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>244774</t>
+          <t>275164</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>290886</t>
+          <t>328281</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>818261</t>
+          <t>663448</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>662366</t>
+          <t>623966</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1136943</t>
+          <t>704592</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>717189</t>
+          <t>830719</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>717189</t>
+          <t>830719</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>717189</t>
+          <t>830719</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1645909</t>
+          <t>1628791</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1645909</t>
+          <t>1628791</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1645909</t>
+          <t>1628791</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,102 +6181,102 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>39411</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>27127</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>55726</t>
+          <t>58773</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>51507</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>38823</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>67059</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>94551</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>75345</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>116989</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
           <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>46285</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>34734</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>62830</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>85695</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>68869</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>107934</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="W52" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6294,102 +6294,102 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>93358</t>
+          <t>100378</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>70990</t>
+          <t>82025</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>113087</t>
+          <t>120209</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>164192</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>143807</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>186952</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>264570</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>237487</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>298730</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>143707</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>117838</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>169300</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>237065</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>199289</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>268386</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>276865</t>
+          <t>309805</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>218882</t>
+          <t>278281</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>317770</t>
+          <t>344022</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>385763</t>
+          <t>429411</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>312078</t>
+          <t>394201</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>427172</t>
+          <t>459904</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>662629</t>
+          <t>739216</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>574616</t>
+          <t>693846</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>724636</t>
+          <t>788008</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>1498798</t>
+          <t>1615067</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1135032</t>
+          <t>1550733</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1636233</t>
+          <t>1684908</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>1835584</t>
+          <t>1762765</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1696913</t>
+          <t>1707913</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>2165482</t>
+          <t>1820765</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>3334382</t>
+          <t>3377832</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3023394</t>
+          <t>3287379</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3656725</t>
+          <t>3460626</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>47,7%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1547522</t>
+          <t>1460664</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1379554</t>
+          <t>1391715</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2002004</t>
+          <t>1529256</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>1242062</t>
+          <t>1318280</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1055393</t>
+          <t>1265172</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1382655</t>
+          <t>1370305</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>2789584</t>
+          <t>2778945</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2528757</t>
+          <t>2698007</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3237245</t>
+          <t>2867238</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>3455954</t>
+          <t>3528958</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3455954</t>
+          <t>3528958</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>3455954</t>
+          <t>3528958</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3653401</t>
+          <t>3726155</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3653401</t>
+          <t>3726155</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3653401</t>
+          <t>3726155</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>7109355</t>
+          <t>7255114</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>7109355</t>
+          <t>7255114</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>7109355</t>
+          <t>7255114</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
